--- a/Research_Evidence_Report.xlsx
+++ b/Research_Evidence_Report.xlsx
@@ -14,17 +14,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>Source</t>
   </si>
   <si>
+    <t>Source Title</t>
+  </si>
+  <si>
+    <t>Name of the Source</t>
+  </si>
+  <si>
+    <t>Source Type</t>
+  </si>
+  <si>
+    <t>Year of Publication</t>
+  </si>
+  <si>
+    <t>Period of the Data Used</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Access Type</t>
+  </si>
+  <si>
+    <t>Source Link</t>
+  </si>
+  <si>
+    <t>Geography Focus</t>
+  </si>
+  <si>
+    <t>Companies Mentioned (Focus)</t>
+  </si>
+  <si>
+    <t>Other Entities Mentioned</t>
+  </si>
+  <si>
     <t>Entities Found (Focus)</t>
   </si>
   <si>
-    <t>Other Entities Mentioned</t>
-  </si>
-  <si>
     <t>Access &amp; Reimbursement (Yes/No)</t>
   </si>
   <si>
@@ -85,64 +115,82 @@
     <t>Overall Summary</t>
   </si>
   <si>
-    <t>https://en.caclp.com/industry-news/2365.html</t>
-  </si>
-  <si>
-    <t>Mindray, Snibe</t>
-  </si>
-  <si>
-    <t>Maccura, Siemens Healthineers, Roche, Abbott Laboratories, Beckman Coulter, Thermo Fisher Scientific, HyTest, Wondfo, Gongdong, Orient Gene, Andon, Zybio, Fosun, YHLO, Autobio, PerkinElmer, Revvity, China IVD companies, GRIP system</t>
+    <t>https://healthcare-in-europe.com/en/news/snibe-makes-an-entry-at-euromedlab.html#:~:text=%E2%80%98Our%20exports%20to%20Europe%20focus,It%E2%80%99s%20perfectly%C2%A0suited%2C%20for%20example%2C%20for</t>
+  </si>
+  <si>
+    <t>Snibe's Entry at EuroMedLab: Strategic Expansion into European IVD Market</t>
+  </si>
+  <si>
+    <t>Healthcare in Europe</t>
+  </si>
+  <si>
+    <t>News Article</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>1995-2013</t>
+  </si>
+  <si>
+    <t>Article detailing Snibe's participation in EuroMedLab 2013, highlighting its product portfolio, European distribution strategy, R&amp;D capabilities, and expansion goals.</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>https://healthcare-in-europe.com/en/news/snibe-makes-an-entry-at-euromedlab.html</t>
+  </si>
+  <si>
+    <t>Europe, China</t>
+  </si>
+  <si>
+    <t>Snibe</t>
+  </si>
+  <si>
+    <t>DiaSystem Scandinavia AB, Medical Systems S.p.A., RAL Técnica para el laboratorio s.a., Labteh export-import doo, University of Shenzhen</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>No information on reimbursement policies, payer support, or pricing approvals was found in the source.</t>
+  </si>
+  <si>
+    <t>No data on healthcare spending, procurement budgets, or investment trends was identified.</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Undoubtedly, it is a prudent decision for Chinese IVD companies to explore opportunities overseas, expanding global business in the context of healthcare reform, centralized procurement, and fierce competition.</t>
-  </si>
-  <si>
-    <t>The paragraph highlights that Chinese IVD firms view European‑style healthcare reform and centralized procurement systems as avenues to access markets, implying that reimbursement and tender mechanisms are key drivers of their overseas strategy.</t>
-  </si>
-  <si>
-    <t>For European expansion, the emphasis on centralized procurement suggests that Chinese suppliers like Mindray and Snibe must align with national tender processes and reimbursement frameworks to secure market entry and volume sales.</t>
-  </si>
-  <si>
-    <t>The mature and stable pricing systems in international markets, along with their vast scale and demands, offer support for enterprises’ development.</t>
-  </si>
-  <si>
-    <t>The statement indicates that stable pricing and large market size abroad provide a reliable revenue base for Chinese IVD firms, reducing financial risk and supporting investment in European market activities.</t>
-  </si>
-  <si>
-    <t>European markets with predictable pricing can justify the capital outlays required for regulatory compliance and distribution, making them financially attractive for Mindray and Snibe.</t>
-  </si>
-  <si>
-    <t>In recent years, several IVD companies have achieved remarkable internationalization milestones.</t>
-  </si>
-  <si>
-    <t>The paragraph lists registration certificates for Mindray (3,914 total, 3,158 overseas) and Snibe (1,493 total, 1,127 overseas), underscoring the importance of product registrations and compliance with destination‑country regulations.</t>
-  </si>
-  <si>
-    <t>Strong registration activity demonstrates that both companies are already navigating EU IVDR requirements, a prerequisite for sustainable European market penetration.</t>
-  </si>
-  <si>
-    <t>Engaged in insightful discussions with Ms. Zhu MENG, the esteemed founder of PureID, who specializes in international medical device registrations, we discovered that a positive trend is highlighted when analyzing the global market and registration data by the GRIP system.</t>
-  </si>
-  <si>
-    <t>The interview reveals a growing demand among international customers for Chinese IVD products, as firms improve quality and seek global recognition, indicating favorable market receptivity.</t>
-  </si>
-  <si>
-    <t>Positive customer perception and demand signal that European labs and hospitals may be increasingly open to adopting Mindray and Snibe offerings, easing entry barriers.</t>
-  </si>
-  <si>
-    <t>Mindray acquired HyTest and notable companies such as Wondfo.</t>
-  </si>
-  <si>
-    <t>Acquisitions of established foreign firms illustrate a strategic move to gain technology, regulatory know‑how, and market footholds.</t>
-  </si>
-  <si>
-    <t>These M&amp;A activities can accelerate Mindray's and Snibe's ability to meet European regulatory standards and build local partnerships, strengthening their expansion prospects.</t>
-  </si>
-  <si>
-    <t>The source documents that Chinese IVD leaders Mindray and Snibe have amassed extensive overseas registration portfolios, reflecting robust regulatory compliance efforts. Their focus on centralized procurement and stable pricing environments aligns with European reimbursement and tender structures, suggesting financial viability. Market interviews indicate growing customer demand for Chinese diagnostic products, while strategic acquisitions (e.g., Mindray's purchase of HyTest) provide technology and regulatory expertise needed for EU entry. Overall, the evidence points to a solid foundation and clear pathways for these companies to expand into Europe, though they must continue to bridge the registration gap relative to global incumbents.</t>
+    <t>2007 TUV certification ISO 9001, ISO 13485;</t>
+  </si>
+  <si>
+    <t>Snibe obtained TUV certifications for ISO 9001 and ISO 13485 in 2007, indicating compliance with international quality and medical device standards. This supports regulatory readiness for European market entry.</t>
+  </si>
+  <si>
+    <t>Certifications demonstrate Snibe's adherence to regulatory requirements, reducing barriers for CE marking and IVDR compliance in Europe.</t>
+  </si>
+  <si>
+    <t>Our exports to Europe focus on immunoassay – the Maglumi 1000, 2000, and 2000 Plus.</t>
+  </si>
+  <si>
+    <t>Snibe exports immunoassay systems to 18 European countries via distributors (e.g., DiaSystem Scandinavia AB in Sweden, Medical Systems S.p.A. in Italy). The company is actively promoting its brand and plans to showcase new products like Maglumi 600 and 4000 at EuroMedLab to target emergency departments and small labs.</t>
+  </si>
+  <si>
+    <t>Distributor partnerships and tailored product offerings indicate growing customer acceptance and strategic targeting of niche European markets.</t>
+  </si>
+  <si>
+    <t>Snibe, Shenzhen New Industries Biomedical Engineering Co., Ltd., is a leading Chinese biomedical technology company dedicated to developing and manufacturing clinical laboratory equipment and reagents.</t>
+  </si>
+  <si>
+    <t>Snibe has 2,000 installations in over 70 countries, with a focus on immunoassay systems. Its R&amp;D innovations include nano magnetic microbeads and organic compound markers. The company aims to become a major global immunoassay supplier within 5-10 years and may establish additional R&amp;D centers outside China.</t>
+  </si>
+  <si>
+    <t>Highlights Snibe's global footprint, technological capabilities, and long-term expansion ambitions, reinforcing its potential for European growth.</t>
+  </si>
+  <si>
+    <t>This source outlines Snibe's strategic push into the European IVD market through participation in EuroMedLab 2013. The company leverages ISO-certified products, distributor networks across 18 European countries, and innovative R&amp;D (e.g., chemiluminescent immunoassay systems) to target laboratories and hospitals. While no direct reimbursement or budget data is provided, Snibe's regulatory compliance and customer-focused approach (e.g., Super POCT devices for emergency departments) suggest strong expansion potential. The absence of Mindray mentions indicates Snibe's independent growth strategy in Europe.</t>
   </si>
 </sst>
 </file>
@@ -487,10 +535,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -560,81 +608,130 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="W2" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId1" location=":~:text=%E2%80%98Our%20exports%20to%20Europe%20focus,It%E2%80%99s%20perfectly%C2%A0suited%2C%20for%20example%2C%20for"/>
+    <hyperlink ref="I2" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
